--- a/AAII_Financials/Quarterly/POM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/POM_QTR_FIN.xlsx
@@ -917,10 +917,10 @@
         <v>2100</v>
       </c>
       <c r="F14" s="3">
-        <v>7400</v>
+        <v>3800</v>
       </c>
       <c r="G14" s="3">
-        <v>7700</v>
+        <v>4000</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>-9900</v>
       </c>
       <c r="F23" s="3">
-        <v>-8900</v>
+        <v>-5200</v>
       </c>
       <c r="G23" s="3">
-        <v>-9200</v>
+        <v>-5500</v>
       </c>
       <c r="H23" s="3">
         <v>-1000</v>
@@ -1294,10 +1294,10 @@
         <v>-9900</v>
       </c>
       <c r="F26" s="3">
-        <v>-8900</v>
+        <v>-5200</v>
       </c>
       <c r="G26" s="3">
-        <v>-9200</v>
+        <v>-5500</v>
       </c>
       <c r="H26" s="3">
         <v>-1000</v>
@@ -1539,10 +1539,10 @@
         <v>-9900</v>
       </c>
       <c r="F33" s="3">
-        <v>-8900</v>
+        <v>-5200</v>
       </c>
       <c r="G33" s="3">
-        <v>-9200</v>
+        <v>-5500</v>
       </c>
       <c r="H33" s="3">
         <v>-1000</v>
@@ -1609,10 +1609,10 @@
         <v>-9900</v>
       </c>
       <c r="F35" s="3">
-        <v>-8900</v>
+        <v>-5200</v>
       </c>
       <c r="G35" s="3">
-        <v>-9200</v>
+        <v>-5500</v>
       </c>
       <c r="H35" s="3">
         <v>-1000</v>
@@ -1778,10 +1778,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12400</v>
+        <v>2800</v>
       </c>
       <c r="E43" s="3">
-        <v>12100</v>
+        <v>2800</v>
       </c>
       <c r="F43" s="3">
         <v>1300</v>
@@ -1848,10 +1848,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>9400</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>9300</v>
       </c>
       <c r="F45" s="3">
         <v>1400</v>
@@ -2298,10 +2298,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8500</v>
+        <v>2100</v>
       </c>
       <c r="E59" s="3">
-        <v>8300</v>
+        <v>2000</v>
       </c>
       <c r="F59" s="3">
         <v>2300</v>
@@ -2989,10 +2989,10 @@
         <v>-9900</v>
       </c>
       <c r="F81" s="3">
-        <v>-8900</v>
+        <v>-5200</v>
       </c>
       <c r="G81" s="3">
-        <v>-9200</v>
+        <v>-5500</v>
       </c>
       <c r="H81" s="3">
         <v>-1000</v>
